--- a/Topics_covered.xlsx
+++ b/Topics_covered.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GLA\FrontEnd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730ECA94-B49B-4CAB-AC0D-9AC2F109EDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF83A256-002B-48AF-8710-CC47C916C82B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3EDEEA53-F3E9-49CB-BD94-85F49F077667}"/>
   </bookViews>
@@ -840,8 +840,8 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="5"/>
